--- a/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
@@ -336,6 +336,62 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4A3AA7"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$H$2:$H$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E34948"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$I$2:$I$6</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="30"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -424,7 +480,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -918,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -960,6 +1016,16 @@
           <t>Bioenergy</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nuclear &amp; other</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -983,6 +1049,12 @@
       <c r="G2" t="n">
         <v>0.066</v>
       </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1006,6 +1078,12 @@
       <c r="G3" t="n">
         <v>0.11572</v>
       </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1029,6 +1107,12 @@
       <c r="G4" t="n">
         <v>0.13461</v>
       </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1052,6 +1136,12 @@
       <c r="G5" t="n">
         <v>0.12861</v>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1074,6 +1164,12 @@
       </c>
       <c r="G6" t="n">
         <v>0.125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -826,7 +827,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -841,7 +841,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -863,7 +862,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -899,7 +897,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -1028,7 +1025,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1057,7 +1054,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1086,7 +1083,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1115,7 +1112,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1144,7 +1141,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bolivia installed generation capacity (CNDC) (to 2025)</a:t>
             </a:r>
           </a:p>
@@ -291,7 +291,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -319,7 +319,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -347,7 +347,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -375,7 +375,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -827,6 +827,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -841,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -862,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -897,6 +900,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -1025,7 +1029,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1054,7 +1058,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1083,7 +1087,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1112,7 +1116,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1141,7 +1145,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -827,7 +828,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -842,7 +842,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -864,7 +863,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -900,7 +898,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -1029,7 +1026,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1058,7 +1055,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1087,7 +1084,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1116,7 +1113,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1145,7 +1142,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/bolivia_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -828,6 +827,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -842,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -863,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -880,7 +882,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Oil_MW = thermal plants listed in CNDC's 'Consumo de Diesel' statistics (Moxos). CNDC publishes those workbooks for 2025, 2026 only; other years use the nearest year's list. Small Beni thermal plants listed by CNDC in 2021-2022 (Rurrenabaque, San Borja, Santa Ana de Yacuma, San Ignacio de Moxos, Yucumo; about 6 MW) are not in those workbooks, so they stay in Gas_MW.</t>
+          <t>Oil_MW = thermal plants listed in CNDC's 'Consumo de Diesel' statistics (Moxos, Rurrenabaque, San Borja, San Ignacio de Moxos, Yucumo). CNDC publishes those workbooks for 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, 2026 only; other years use the nearest year's list. Small Beni thermal plants listed by CNDC in 2021-2022 (Rurrenabaque, San Borja, Santa Ana de Yacuma, San Ignacio de Moxos, Yucumo; about 6 MW) are not in those workbooks, so they stay in Gas_MW.</t>
         </is>
       </c>
     </row>
@@ -898,6 +900,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -1026,14 +1029,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
         <v>0.7348300000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.47075</v>
+        <v>2.46607</v>
       </c>
       <c r="D2" t="n">
         <v>0.1278</v>
@@ -1042,7 +1045,7 @@
         <v>0.16508</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02528</v>
+        <v>0.02996</v>
       </c>
       <c r="G2" t="n">
         <v>0.066</v>
@@ -1055,14 +1058,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
         <v>0.73485</v>
       </c>
       <c r="C3" t="n">
-        <v>2.46782</v>
+        <v>2.46314</v>
       </c>
       <c r="D3" t="n">
         <v>0.1314</v>
@@ -1071,7 +1074,7 @@
         <v>0.16508</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0057</v>
+        <v>0.01038</v>
       </c>
       <c r="G3" t="n">
         <v>0.11572</v>
@@ -1084,7 +1087,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1113,7 +1116,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1142,7 +1145,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">
@@ -1250,7 +1253,7 @@
         <v>734.83</v>
       </c>
       <c r="C2" t="n">
-        <v>2470.75</v>
+        <v>2466.07</v>
       </c>
       <c r="D2" t="n">
         <v>127.8</v>
@@ -1265,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>25.28</v>
+        <v>29.96</v>
       </c>
       <c r="I2" t="n">
         <v>66</v>
@@ -1285,7 +1288,7 @@
         <v>734.85</v>
       </c>
       <c r="C3" t="n">
-        <v>2467.82</v>
+        <v>2463.14</v>
       </c>
       <c r="D3" t="n">
         <v>131.4</v>
@@ -1300,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7</v>
+        <v>10.38</v>
       </c>
       <c r="I3" t="n">
         <v>115.72</v>
